--- a/running times.xlsx
+++ b/running times.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Computer\personal\PhD\Tasks\Implementation\Termgraph 2026 implementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56F8DE6E-34E9-4633-BF71-33C1578B52EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98552C4A-7DE6-450F-8C3E-ECDDC0E79601}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A691C0C1-7CCF-4F42-A312-FF41E8D046DD}"/>
   </bookViews>
@@ -452,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE548D90-257D-4A3C-875A-7309F5E9AC22}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -606,6 +606,18 @@
         <v>4.1232604373757447</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <f>5.9/2.4</f>
+        <v>2.4583333333333335</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <f>0.55*55</f>
+        <v>30.250000000000004</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
